--- a/artfynd/A 9826-2020 artfynd.xlsx
+++ b/artfynd/A 9826-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9826-2020 artfynd.xlsx
+++ b/artfynd/A 9826-2020 artfynd.xlsx
@@ -1985,7 +1985,7 @@
         <v>102627385</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567167.2067740512</v>
+        <v>567167</v>
       </c>
       <c r="R13" t="n">
-        <v>6947459.105372344</v>
+        <v>6947459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,19 +2060,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2752,7 +2742,7 @@
         <v>102627382</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2794,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567156.0300085586</v>
+        <v>567156</v>
       </c>
       <c r="R19" t="n">
-        <v>6947487.851824289</v>
+        <v>6947488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2827,19 +2817,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 9826-2020 artfynd.xlsx
+++ b/artfynd/A 9826-2020 artfynd.xlsx
@@ -1985,7 +1985,7 @@
         <v>102627385</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>102627382</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 9826-2020 artfynd.xlsx
+++ b/artfynd/A 9826-2020 artfynd.xlsx
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Erland Lindblad</t>
+          <t>Erland Lindblad, Carl Jansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Erland Lindblad</t>
+          <t>Erland Lindblad, Carl Jansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 9826-2020 artfynd.xlsx
+++ b/artfynd/A 9826-2020 artfynd.xlsx
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Carl Jansson</t>
+          <t>Carl Jansson, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Carl Jansson</t>
+          <t>Carl Jansson, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 9826-2020 artfynd.xlsx
+++ b/artfynd/A 9826-2020 artfynd.xlsx
@@ -1985,7 +1985,7 @@
         <v>102627385</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>102627382</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
